--- a/rover_parts_list.xlsx
+++ b/rover_parts_list.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
   <si>
     <t xml:space="preserve">Produkt</t>
   </si>
@@ -76,15 +76,15 @@
     <t xml:space="preserve">Grüne LED</t>
   </si>
   <si>
+    <t xml:space="preserve">RGB LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLED Display</t>
+  </si>
+  <si>
     <t xml:space="preserve">TODO</t>
   </si>
   <si>
-    <t xml:space="preserve">RGB LED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLED Display</t>
-  </si>
-  <si>
     <t xml:space="preserve">Akku</t>
   </si>
   <si>
@@ -115,31 +115,31 @@
     <t xml:space="preserve">Pollin</t>
   </si>
   <si>
-    <t xml:space="preserve">TODO, Schule</t>
+    <t xml:space="preserve">evtl. Schule</t>
   </si>
   <si>
     <t xml:space="preserve">USB-Kabel</t>
   </si>
   <si>
-    <t xml:space="preserve">JST-Stecker 2pol für Akku auf Platine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JST-Buchse 2pol für Akku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JST-Stecker 4pol für Li-ion safe</t>
+    <t xml:space="preserve">JST-Stecker XH 2pol für Akku auf Platine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JST-Buchse XH 2pol für Akku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JST-Stecker 4pol für Li-ion safe (Platine)</t>
   </si>
   <si>
     <t xml:space="preserve">optional, kann auch gelötet werden</t>
   </si>
   <si>
-    <t xml:space="preserve">JST-Buchse 4pol für Li-ion safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontakte weibl.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontakte männl.</t>
+    <t xml:space="preserve">JST-Buchse 4pol für Li-ion safe (Modul)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontakte XH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sind erstmal vorhanden; gibt es auch bei Eckstein</t>
   </si>
   <si>
     <t xml:space="preserve">Diode 1N5817</t>
@@ -218,8 +218,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -412,483 +416,476 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>6.03</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <f aca="false">B2*C2</f>
         <v>6.03</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="0" t="n">
-        <f aca="false">SUM(D2:D101)</f>
-        <v>19.482</v>
+      <c r="H2" s="1" t="n">
+        <f aca="false">SUM(D2:D100)</f>
+        <v>19.9916</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>0.44</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <f aca="false">B3*C3</f>
         <v>0.44</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>0.69</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <f aca="false">B4*C4</f>
         <v>0.69</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>1.1</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <f aca="false">B5*C5</f>
         <v>1.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>1.92</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">B6*C6</f>
         <v>3.84</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>2.06</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <f aca="false">B7*C7</f>
         <v>2.06</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <f aca="false">B8*C8</f>
         <v>0.5</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="0" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="B9" s="1" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <f aca="false">B9*C9</f>
-        <v>0.012</v>
-      </c>
-      <c r="F9" s="0" t="s">
+        <v>0.094</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="B10" s="1" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <f aca="false">B10*C10</f>
+        <v>0.2576</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <f aca="false">B10*C10</f>
-        <v>0.8</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>2.31</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <f aca="false">B11*C11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>18</v>
+      <c r="F11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="C12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <f aca="false">B12*C12</f>
         <v>0.5</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="B13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <f aca="false">B13*C13</f>
         <v>1</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <f aca="false">B14*C14</f>
         <v>1</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="B15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <f aca="false">B15*C15</f>
         <v>1</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>0.48</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="0" t="n">
+      <c r="C16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <f aca="false">B16*C16</f>
         <v>0.48</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C17" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <f aca="false">B17*C17</f>
         <v>0</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C18" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <f aca="false">B18*C18</f>
         <v>0</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="0" t="n">
+      <c r="B19" s="0" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <f aca="false">B19*C19</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="0" t="s">
+        <v>0.17</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="0" t="n">
+      <c r="B20" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="n">
         <f aca="false">B20*C20</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="0" t="s">
+        <v>0.05</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="0" t="n">
+      <c r="B21" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="n">
         <f aca="false">B21*C21</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="0" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="0" t="n">
+      <c r="B22" s="0" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <f aca="false">B22*C22</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="0" t="s">
+        <v>0.07</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="B23" s="0" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C23" s="1" t="n">
         <f aca="false">4*C21+2*C19</f>
         <v>6</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="1" t="n">
         <f aca="false">B23*C23</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="0" t="s">
+        <v>0.48</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="0" t="n">
-        <f aca="false">4*C22+2*C20</f>
-        <v>6</v>
-      </c>
-      <c r="D24" s="0" t="n">
+    </row>
+    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1" t="n">
         <f aca="false">B24*C24</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="0" t="n">
         <v>0.03</v>
       </c>
-      <c r="C25" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="0" t="n">
-        <f aca="false">B25*C25</f>
-        <v>0.03</v>
-      </c>
-      <c r="E25" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="Mouser"/>
@@ -897,7 +894,17 @@
     <hyperlink ref="E6" r:id="rId4" display="Christian"/>
     <hyperlink ref="E7" r:id="rId5" display="Christian"/>
     <hyperlink ref="E8" r:id="rId6" display="Medicometer"/>
-    <hyperlink ref="E16" r:id="rId7" display="Reichelt"/>
+    <hyperlink ref="E9" r:id="rId7" display="Mouser"/>
+    <hyperlink ref="E10" r:id="rId8" display="Mouser"/>
+    <hyperlink ref="E16" r:id="rId9" display="Reichelt"/>
+    <hyperlink ref="E17" r:id="rId10" display="Pollin"/>
+    <hyperlink ref="E18" r:id="rId11" display="Pollin"/>
+    <hyperlink ref="E19" r:id="rId12" display="Reichelt"/>
+    <hyperlink ref="E20" r:id="rId13" display="Reichelt"/>
+    <hyperlink ref="E21" r:id="rId14" display="Reichelt"/>
+    <hyperlink ref="E22" r:id="rId15" display="Reichelt"/>
+    <hyperlink ref="E23" r:id="rId16" display="Reichelt"/>
+    <hyperlink ref="E24" r:id="rId17" display="Pollin"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
